--- a/M2. Statistica & Excel/PraticaW1D1_GGabriele.xlsx
+++ b/M2. Statistica & Excel/PraticaW1D1_GGabriele.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Desktop\Epicode-Dapt0326\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Desktop\Epicode-Dapt0326\M2. Statistica &amp; Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB26A2E-1B79-4333-B748-F85BFE7B18D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48520790-CBE4-4F9B-84C5-FBAD1A735382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="1725" windowWidth="24240" windowHeight="13020" xr2:uid="{CC2D0ADA-4E80-42B2-8D69-B90DD28C34B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC2D0ADA-4E80-42B2-8D69-B90DD28C34B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
   <si>
     <t>Dataset</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>La deviazione standard aumenta in modo drastico (da 3.50 a 18.52). Così come la media, anche la deviazione standard è fortemente sensibile ai valori anomali, poiché si basa sugli scarti dalla media</t>
+  </si>
+  <si>
+    <t>OUTLIER</t>
   </si>
 </sst>
 </file>
@@ -651,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B321869A-40B5-42E3-B355-DD29B761D376}">
-  <dimension ref="B2:L53"/>
+  <dimension ref="B2:M53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -969,7 +972,7 @@
         <v>11.111111111111104</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>12</v>
       </c>
@@ -995,7 +998,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="H18">
         <v>3</v>
       </c>
@@ -1007,7 +1010,7 @@
         <v>29.25</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
         <v>16</v>
       </c>
@@ -1016,12 +1019,12 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1038,8 +1041,15 @@
         <f>J17-1.5*J20</f>
         <v>18.625</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" t="str" cm="1">
+        <f t="array" ref="M23">_xlfn.TEXTJOIN("; ",TRUE,_xlfn._xlws.FILTER(Tabella1[Voti studenti],(Tabella1[Voti studenti] &lt; J23)+(Tabella1[Voti studenti] &gt; J24),"") )</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>18</v>
       </c>
@@ -1059,7 +1069,7 @@
         <v>35.625</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>22</v>
       </c>
@@ -1074,7 +1084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>26</v>
       </c>
@@ -1089,7 +1099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="E27">
         <v>0</v>
       </c>
@@ -1097,7 +1107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>21</v>
       </c>
